--- a/human_validation/judge/kor/judge_D004_S002_P002__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D004_S002_P002__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,103 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 1년 넘게 회사에서 일어나고 있는 일을 누군가 진지하게 받아들여 주길 바라면서 지내왔는데, 그게 잘 안 돼서 오게 됐어요. 새로 바뀐 티켓 순환 방식이랑 이 보안 감사들 있잖아요—저는 그게 저를 상대로 무슨 서류상 증거를 만들려고 쓰이고 있다고 생각해요. 관리자들은 계속 로그 기록을 보여주면서 그냥 정책일 뿐이라고 하는데, 저는 그게 전부는 아닌 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 주변에 아무도 없을 때 목소리나 속삭임, 혹은 다른 소리를 들으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 아니요, 혼자 있을 때 그런 목소리나 소리를 들은 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 누군가 본인의 생각을 방해하고 있다거나, 외부의 힘이 본인의 마음이나 몸을 조종하고 있다고 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 아니요, 제 마음이나 몸을 뭔가가 조종하고 있다는 느낌은 없어요. 제 생각은 온전히 제 것처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 직장 밖에서는 친구나 가족, 파트너를 믿을 수 있는지 자주 의심하게 되시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 정확히 무슨 말씀이신지 잘 모르겠어요. 직장 밖에서는 그게 문제가 된다고 딱히 느껴본 적이 없어서요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>진단명: 망상장애 (D004)
 인구통계: 성별 남성 / 나이 60 / 직업상태 computer support specialist / 최종학력 학사
@@ -575,152 +663,29 @@
 증상 지속 기간: 1 year and 2 months
 추가 요건: Functioning is not markedly impaired apart from the impact of the delusion(s) or its ramifications
 주호소 증상 코드: S019
-배경 서술: 오랫동안 안정적이었던 호셀리토의 IT 업무는 회사가 교대 근무 형태의 하이브리드 근무제로 바뀌면서 달라졌다. 업무 시간 외 지원 티켓 처리, 더 엄격해진 보안 규정, 그리고 후배 직원들과의 비공식적인 멘토링 시간이 줄어든 것이 그 배경이었다. 이후 1년 2개월 동안 그는 직장에서 벌어지고 있는 일에 대해 고정된 믿음을 형성했고, 상사들이 로그 기록과 정책 문서를 제시하고 직접 안심시켜 주어도 그 믿음은 흔들리지 않았다. 그는 여전히 기술적으로 유능하게 업무를 수행했지만, 그 믿음은 점차 회의, 문서 작업, 그리고 특정 네트워크 프로젝트에 대한 협업 의지에까지 영향을 미치기 시작했다. 그는 회사에 중재를 요청한 뒤 직원 지원 프로그램을 통해 정신과 진료를 받게 되었으며, 아내 역시 그에게 이번 진료를 계기로 직장과 가정의 평화를 모두 지켜보라고 권했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 1년 넘게 회사에서 일어나고 있는 일을 누군가 진지하게 받아들여 주길 바라면서 지내왔는데, 그게 잘 안 돼서 오게 됐어요. 새로 바뀐 티켓 순환 방식이랑 이 보안 감사들 있잖아요—저는 그게 저를 상대로 무슨 서류상 증거를 만들려고 쓰이고 있다고 생각해요. 관리자들은 계속 로그 기록을 보여주면서 그냥 정책일 뿐이라고 하는데, 저는 그게 전부는 아닌 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 주변에 아무도 없을 때 목소리나 속삭임, 혹은 다른 소리를 들으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 아니요, 혼자 있을 때 그런 목소리나 소리를 들은 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 누군가 본인의 생각을 방해하고 있다거나, 외부의 힘이 본인의 마음이나 몸을 조종하고 있다고 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 아니요, 제 마음이나 몸을 뭔가가 조종하고 있다는 느낌은 없어요. 제 생각은 온전히 제 것처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 직장 밖에서는 친구나 가족, 파트너를 믿을 수 있는지 자주 의심하게 되시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 정확히 무슨 말씀이신지 잘 모르겠어요. 직장 밖에서는 그게 문제가 된다고 딱히 느껴본 적이 없어서요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+배경 서술: 오랫동안 안정적이었던 호셀리토의 IT 업무는 회사가 교대 근무 형태의 하이브리드 근무제로 바뀌면서 달라졌다. 업무 시간 외 지원 티켓 처리, 더 엄격해진 보안 규정, 그리고 후배 직원들과의 비공식적인 멘토링 시간이 줄어든 것이 그 배경이었다. 이후 1년 2개월 동안 그는 직장에서 벌어지고 있는 일에 대해 고정된 믿음을 형성했고, 상사들이 로그 기록과 정책 문서를 제시하고 직접 안심시켜 주어도 그 믿음은 흔들리지 않았다. 그는 여전히 기술적으로 유능하게 업무를 수행했지만, 그 믿음은 점차 회의, 문서 작업, 그리고 특정 네트워크 프로젝트에 대한 협업 의지에까지 영향을 미치기 시작했다. 그는 회사에 중재를 요청한 뒤 직원 지원 프로그램을 통해 정신과 진료를 받게 되었으며, 아내 역시 그에게 이번 진료를 계기로 직장과 가정의 평화를 모두 지켜보라고 권했다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.</t>
+        </is>
+      </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 망상장애 (D004, ICD: F22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 망상장애 (D004, ICD: F22)
+지속 기간 요건: 있음
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: delusions (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D004_S002_P002__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D004_S002_P002__gemini-3.8-flash_kor.xlsx
@@ -649,6 +649,11 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -681,11 +686,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D004_S002_P002__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D004_S002_P002__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.6964</v>
+        <v>0.7083</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.7917</v>
+        <v>0.7083</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.8333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.6667</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
